--- a/jpcore-r4/feature/swg2-dental-eCS-md-update/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS-md-update/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7190" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7190" uniqueCount="738">
   <si>
     <t>Property</t>
   </si>
@@ -1402,6 +1402,9 @@
   </si>
   <si>
     <t>Observation.bodySite.extension</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>Extension</t>
@@ -11713,7 +11716,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>94</v>
+        <v>447</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>82</v>
@@ -11731,10 +11734,10 @@
         <v>140</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11820,13 +11823,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>446</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11848,16 +11851,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11942,10 +11945,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12060,10 +12063,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12089,10 +12092,10 @@
         <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12178,10 +12181,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12207,13 +12210,13 @@
         <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -12221,7 +12224,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>83</v>
@@ -12263,7 +12266,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>94</v>
@@ -12298,10 +12301,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12327,10 +12330,10 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12361,7 +12364,7 @@
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12379,7 +12382,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12414,10 +12417,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12532,10 +12535,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12652,10 +12655,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12774,10 +12777,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12892,10 +12895,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13012,10 +13015,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13057,7 +13060,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>83</v>
@@ -13134,10 +13137,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13254,10 +13257,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13374,10 +13377,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13494,10 +13497,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13616,10 +13619,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13738,20 +13741,20 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>446</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>82</v>
@@ -13766,13 +13769,13 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13858,10 +13861,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13976,10 +13979,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14005,10 +14008,10 @@
         <v>140</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14094,13 +14097,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>83</v>
@@ -14125,10 +14128,10 @@
         <v>140</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14214,10 +14217,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14332,10 +14335,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14361,10 +14364,10 @@
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14450,10 +14453,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14479,13 +14482,13 @@
         <v>108</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14493,7 +14496,7 @@
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>83</v>
@@ -14535,7 +14538,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>94</v>
@@ -14570,10 +14573,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14599,10 +14602,10 @@
         <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14633,7 +14636,7 @@
       </c>
       <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14651,7 +14654,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14686,13 +14689,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>83</v>
@@ -14717,10 +14720,10 @@
         <v>140</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14806,10 +14809,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14924,10 +14927,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14953,10 +14956,10 @@
         <v>140</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15042,10 +15045,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15071,13 +15074,13 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15085,7 +15088,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>83</v>
@@ -15127,7 +15130,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>94</v>
@@ -15162,10 +15165,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15191,10 +15194,10 @@
         <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15245,7 +15248,7 @@
         <v>83</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15280,13 +15283,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>83</v>
@@ -15311,10 +15314,10 @@
         <v>140</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15400,10 +15403,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15518,10 +15521,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15638,13 +15641,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>83</v>
@@ -15669,10 +15672,10 @@
         <v>140</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15758,10 +15761,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15876,10 +15879,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15905,10 +15908,10 @@
         <v>140</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15994,10 +15997,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16023,13 +16026,13 @@
         <v>108</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -16037,7 +16040,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>83</v>
@@ -16079,7 +16082,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>94</v>
@@ -16114,10 +16117,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16143,10 +16146,10 @@
         <v>191</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -16197,7 +16200,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16232,13 +16235,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>83</v>
@@ -16263,10 +16266,10 @@
         <v>140</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16352,10 +16355,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16470,10 +16473,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16499,10 +16502,10 @@
         <v>140</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16588,10 +16591,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16617,13 +16620,13 @@
         <v>108</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -16631,7 +16634,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>83</v>
@@ -16673,7 +16676,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>94</v>
@@ -16708,10 +16711,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16737,10 +16740,10 @@
         <v>191</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16791,7 +16794,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16826,13 +16829,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
@@ -16857,10 +16860,10 @@
         <v>140</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16946,10 +16949,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17064,10 +17067,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17184,10 +17187,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>407</v>
@@ -17215,10 +17218,10 @@
         <v>140</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17304,10 +17307,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17422,10 +17425,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17451,10 +17454,10 @@
         <v>140</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -17540,10 +17543,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17569,13 +17572,13 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -17625,7 +17628,7 @@
         <v>83</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>94</v>
@@ -17660,10 +17663,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17686,13 +17689,13 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -17743,7 +17746,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17778,10 +17781,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17807,13 +17810,13 @@
         <v>108</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17821,7 +17824,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>83</v>
@@ -17863,7 +17866,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>94</v>
@@ -17898,10 +17901,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17924,13 +17927,13 @@
         <v>83</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17981,7 +17984,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18016,13 +18019,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>83</v>
@@ -18047,10 +18050,10 @@
         <v>140</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -18136,10 +18139,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18254,10 +18257,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18283,10 +18286,10 @@
         <v>140</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -18372,10 +18375,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18401,13 +18404,13 @@
         <v>108</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18415,7 +18418,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>83</v>
@@ -18457,7 +18460,7 @@
         <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>94</v>
@@ -18492,10 +18495,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18521,10 +18524,10 @@
         <v>191</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18575,7 +18578,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -18610,10 +18613,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18639,13 +18642,13 @@
         <v>108</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -18653,7 +18656,7 @@
       </c>
       <c r="Q134" s="2"/>
       <c r="R134" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="S134" t="s" s="2">
         <v>83</v>
@@ -18695,7 +18698,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>94</v>
@@ -18730,10 +18733,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18756,13 +18759,13 @@
         <v>83</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18813,7 +18816,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -18848,13 +18851,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>83</v>
@@ -18879,10 +18882,10 @@
         <v>140</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18968,10 +18971,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19086,10 +19089,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19115,10 +19118,10 @@
         <v>140</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -19204,10 +19207,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19233,13 +19236,13 @@
         <v>108</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19247,7 +19250,7 @@
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>83</v>
@@ -19289,7 +19292,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>94</v>
@@ -19324,10 +19327,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19353,10 +19356,10 @@
         <v>191</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -19407,7 +19410,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19442,10 +19445,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19560,10 +19563,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19680,10 +19683,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19755,7 +19758,7 @@
         <v>83</v>
       </c>
       <c r="AB143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AC143" s="2"/>
       <c r="AD143" t="s" s="2">
@@ -19800,13 +19803,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D144" t="s" s="2">
         <v>83</v>
@@ -19831,10 +19834,10 @@
         <v>221</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>224</v>
@@ -19869,7 +19872,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>83</v>
@@ -19922,10 +19925,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20040,10 +20043,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20160,10 +20163,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20205,7 +20208,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>83</v>
@@ -20282,10 +20285,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20402,10 +20405,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20522,10 +20525,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20642,10 +20645,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20764,13 +20767,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>83</v>
@@ -20795,10 +20798,10 @@
         <v>221</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>224</v>
@@ -20833,7 +20836,7 @@
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>83</v>
@@ -20886,10 +20889,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21004,10 +21007,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21124,10 +21127,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21169,7 +21172,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>83</v>
@@ -21246,10 +21249,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21366,10 +21369,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21486,10 +21489,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21606,10 +21609,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21728,10 +21731,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21850,10 +21853,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21879,13 +21882,13 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -21893,7 +21896,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>83</v>
@@ -21935,7 +21938,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>94</v>
@@ -21970,10 +21973,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21996,13 +21999,13 @@
         <v>83</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -22053,7 +22056,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22088,10 +22091,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22210,10 +22213,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22332,10 +22335,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22361,16 +22364,16 @@
         <v>191</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>83</v>
@@ -22398,10 +22401,10 @@
         <v>326</v>
       </c>
       <c r="Y165" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Z165" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AA165" t="s" s="2">
         <v>83</v>
@@ -22419,7 +22422,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -22440,10 +22443,10 @@
         <v>83</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>83</v>
@@ -22454,10 +22457,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22480,16 +22483,16 @@
         <v>83</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22539,7 +22542,7 @@
         <v>83</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -22557,27 +22560,27 @@
         <v>83</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22600,16 +22603,16 @@
         <v>83</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -22659,7 +22662,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -22677,27 +22680,27 @@
         <v>83</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22720,19 +22723,19 @@
         <v>83</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>83</v>
@@ -22781,7 +22784,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -22793,7 +22796,7 @@
         <v>83</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>83</v>
@@ -22802,10 +22805,10 @@
         <v>83</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>83</v>
@@ -22816,10 +22819,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22934,10 +22937,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23054,14 +23057,14 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -23083,10 +23086,10 @@
         <v>140</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>143</v>
@@ -23141,7 +23144,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -23176,10 +23179,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23202,13 +23205,13 @@
         <v>83</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23259,7 +23262,7 @@
         <v>83</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -23268,7 +23271,7 @@
         <v>94</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>106</v>
@@ -23280,10 +23283,10 @@
         <v>83</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>83</v>
@@ -23294,10 +23297,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23320,13 +23323,13 @@
         <v>83</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23377,7 +23380,7 @@
         <v>83</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -23386,7 +23389,7 @@
         <v>94</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>106</v>
@@ -23398,10 +23401,10 @@
         <v>83</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>83</v>
@@ -23412,10 +23415,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23441,16 +23444,16 @@
         <v>191</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>83</v>
@@ -23478,10 +23481,10 @@
         <v>118</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>83</v>
@@ -23499,7 +23502,7 @@
         <v>83</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -23517,10 +23520,10 @@
         <v>83</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AN174" t="s" s="2">
         <v>427</v>
@@ -23534,10 +23537,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23563,16 +23566,16 @@
         <v>191</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>83</v>
@@ -23600,10 +23603,10 @@
         <v>326</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>83</v>
@@ -23621,7 +23624,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -23639,10 +23642,10 @@
         <v>83</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>427</v>
@@ -23656,10 +23659,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23682,17 +23685,17 @@
         <v>83</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P176" t="s" s="2">
         <v>83</v>
@@ -23741,7 +23744,7 @@
         <v>83</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -23765,7 +23768,7 @@
         <v>83</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>83</v>
@@ -23776,10 +23779,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23805,10 +23808,10 @@
         <v>208</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -23859,7 +23862,7 @@
         <v>83</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -23880,10 +23883,10 @@
         <v>83</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>83</v>
@@ -23894,10 +23897,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23920,16 +23923,16 @@
         <v>95</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -23979,7 +23982,7 @@
         <v>83</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -24000,10 +24003,10 @@
         <v>83</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>83</v>
@@ -24014,10 +24017,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24040,16 +24043,16 @@
         <v>95</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -24099,7 +24102,7 @@
         <v>83</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -24120,10 +24123,10 @@
         <v>83</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -24134,10 +24137,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24160,19 +24163,19 @@
         <v>95</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>83</v>
@@ -24221,7 +24224,7 @@
         <v>83</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -24242,10 +24245,10 @@
         <v>83</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>83</v>
@@ -24256,10 +24259,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24374,10 +24377,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24494,14 +24497,14 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
@@ -24523,10 +24526,10 @@
         <v>140</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>143</v>
@@ -24581,7 +24584,7 @@
         <v>83</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -24616,10 +24619,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24645,13 +24648,13 @@
         <v>191</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="O184" t="s" s="2">
         <v>325</v>
@@ -24703,7 +24706,7 @@
         <v>83</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>94</v>
@@ -24721,7 +24724,7 @@
         <v>83</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>331</v>
@@ -24738,10 +24741,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24764,16 +24767,16 @@
         <v>95</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O185" t="s" s="2">
         <v>402</v>
@@ -24825,7 +24828,7 @@
         <v>83</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -24843,7 +24846,7 @@
         <v>83</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>406</v>
@@ -24860,10 +24863,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24889,13 +24892,13 @@
         <v>191</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O186" t="s" s="2">
         <v>412</v>
@@ -24947,7 +24950,7 @@
         <v>83</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -24982,10 +24985,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25011,16 +25014,16 @@
         <v>191</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>83</v>
@@ -25069,7 +25072,7 @@
         <v>83</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25104,10 +25107,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25133,16 +25136,16 @@
         <v>84</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>83</v>
@@ -25191,7 +25194,7 @@
         <v>83</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -25212,10 +25215,10 @@
         <v>83</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>83</v>
